--- a/cypress/downloads/Client Follow Ups_20251203.xlsx
+++ b/cypress/downloads/Client Follow Ups_20251203.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Mobile Number</t>
   </si>
@@ -32,16 +32,25 @@
     <t>Sent Date</t>
   </si>
   <si>
+    <t>201273196467</t>
+  </si>
+  <si>
+    <t>TND</t>
+  </si>
+  <si>
+    <t>hello_world</t>
+  </si>
+  <si>
+    <t>delivered</t>
+  </si>
+  <si>
+    <t>03/12/2025 | 4:08 PM</t>
+  </si>
+  <si>
     <t>201289055472</t>
   </si>
   <si>
-    <t>TND</t>
-  </si>
-  <si>
-    <t>hello_world</t>
-  </si>
-  <si>
-    <t>delivered</t>
+    <t>read</t>
   </si>
   <si>
     <t>03/12/2025 | 11:48 AM</t>
@@ -56,13 +65,7 @@
     <t>02/12/2025 | 6:19 PM</t>
   </si>
   <si>
-    <t>read</t>
-  </si>
-  <si>
     <t>02/12/2025 | 12:29 PM</t>
-  </si>
-  <si>
-    <t>201273196467</t>
   </si>
   <si>
     <t>01/12/2025 | 2:45 PM</t>
@@ -242,7 +245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -294,16 +297,16 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
@@ -316,12 +319,12 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -330,16 +333,16 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
@@ -348,7 +351,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
@@ -366,7 +369,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2" t="s">
@@ -375,7 +378,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>7</v>
@@ -384,7 +387,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
@@ -402,7 +405,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
@@ -411,7 +414,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
@@ -420,7 +423,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
@@ -429,7 +432,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>7</v>
@@ -438,7 +441,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
@@ -447,7 +450,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>7</v>
@@ -456,7 +459,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
@@ -465,7 +468,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -474,7 +477,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
@@ -483,7 +486,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>7</v>
@@ -492,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
@@ -501,7 +504,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>7</v>
@@ -510,7 +513,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
@@ -519,7 +522,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>7</v>
@@ -528,7 +531,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
@@ -537,54 +540,54 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
@@ -602,7 +605,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
@@ -620,7 +623,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
@@ -629,7 +632,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
@@ -638,7 +641,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
@@ -647,7 +650,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>7</v>
@@ -656,16 +659,16 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -674,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
@@ -683,164 +686,164 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
@@ -852,53 +855,53 @@
         <v>11</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
@@ -909,10 +912,10 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
@@ -921,20 +924,38 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
